--- a/storage/app/public/data warga.xlsx
+++ b/storage/app/public/data warga.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JEMAN\Documents\kuliah\skripsi\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apache24\htdocs\dashboard-digital\public\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1EBE1B-FDB8-4B79-8194-8CDC493EE953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C31C066-EC9D-4DA0-8B9C-F6D4D9211347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="343">
   <si>
     <t>NIK</t>
   </si>
@@ -894,27 +894,9 @@
     <t>Jl. Kramat Pulo 9B</t>
   </si>
   <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>011</t>
-  </si>
-  <si>
-    <t>006</t>
-  </si>
-  <si>
-    <t>007</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
-    <t>004</t>
-  </si>
-  <si>
     <t>WNI</t>
   </si>
   <si>
@@ -984,9 +966,6 @@
     <t>Jakarta</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>29/02/1970</t>
   </si>
   <si>
@@ -1057,6 +1036,30 @@
   </si>
   <si>
     <t>19/27/1965</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>027</t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1500,7 @@
     <col min="12" max="12" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.5546875" customWidth="1"/>
+    <col min="15" max="15" width="4.88671875" customWidth="1"/>
     <col min="16" max="16" width="7" customWidth="1"/>
     <col min="17" max="18" width="3.77734375" bestFit="1" customWidth="1"/>
   </cols>
@@ -1528,10 +1531,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
@@ -1543,7 +1546,7 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>11</v>
@@ -1563,43 +1566,43 @@
         <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H2" t="s">
         <v>295</v>
       </c>
-      <c r="G2" t="s">
-        <v>332</v>
-      </c>
-      <c r="H2" t="s">
-        <v>301</v>
-      </c>
       <c r="I2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J2" s="5">
         <v>26441</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N2" t="s">
-        <v>323</v>
-      </c>
-      <c r="O2" t="s">
-        <v>288</v>
+        <v>316</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -1613,43 +1616,43 @@
         <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G3" t="s">
+        <v>326</v>
+      </c>
+      <c r="H3" t="s">
         <v>295</v>
       </c>
-      <c r="G3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H3" t="s">
-        <v>301</v>
-      </c>
       <c r="I3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J3" s="5">
         <v>27708</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L3" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N3" t="s">
-        <v>324</v>
-      </c>
-      <c r="O3" t="s">
-        <v>288</v>
+        <v>317</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
@@ -1663,43 +1666,43 @@
         <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F4" t="s">
+        <v>289</v>
+      </c>
+      <c r="G4" t="s">
+        <v>327</v>
+      </c>
+      <c r="H4" t="s">
         <v>295</v>
       </c>
-      <c r="G4" t="s">
-        <v>334</v>
-      </c>
-      <c r="H4" t="s">
-        <v>301</v>
-      </c>
       <c r="I4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J4" s="5">
         <v>35464</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L4" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N4" t="s">
-        <v>325</v>
-      </c>
-      <c r="O4" t="s">
-        <v>288</v>
+        <v>318</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
@@ -1713,43 +1716,43 @@
         <v>174</v>
       </c>
       <c r="D5" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E5" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H5" t="s">
         <v>295</v>
       </c>
-      <c r="G5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H5" t="s">
-        <v>301</v>
-      </c>
       <c r="I5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J5" s="5">
         <v>39920</v>
       </c>
       <c r="K5" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L5" t="s">
         <v>315</v>
       </c>
-      <c r="L5" t="s">
-        <v>322</v>
-      </c>
       <c r="M5" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N5" t="s">
-        <v>325</v>
-      </c>
-      <c r="O5" t="s">
-        <v>288</v>
+        <v>318</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -1763,43 +1766,43 @@
         <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E6" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F6" t="s">
+        <v>289</v>
+      </c>
+      <c r="G6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H6" t="s">
         <v>295</v>
       </c>
-      <c r="G6" t="s">
-        <v>334</v>
-      </c>
-      <c r="H6" t="s">
-        <v>301</v>
-      </c>
       <c r="I6" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J6" s="5">
         <v>40054</v>
       </c>
       <c r="K6" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L6" t="s">
         <v>315</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>322</v>
       </c>
-      <c r="M6" t="s">
-        <v>329</v>
-      </c>
       <c r="N6" t="s">
-        <v>325</v>
-      </c>
-      <c r="O6" t="s">
-        <v>288</v>
+        <v>318</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P6" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
@@ -1813,43 +1816,43 @@
         <v>176</v>
       </c>
       <c r="D7" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E7" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F7" t="s">
+        <v>289</v>
+      </c>
+      <c r="G7" t="s">
+        <v>325</v>
+      </c>
+      <c r="H7" t="s">
         <v>295</v>
       </c>
-      <c r="G7" t="s">
-        <v>332</v>
-      </c>
-      <c r="H7" t="s">
-        <v>301</v>
-      </c>
       <c r="I7" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J7" s="5">
         <v>28357</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L7" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M7" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N7" t="s">
-        <v>323</v>
-      </c>
-      <c r="O7" t="s">
-        <v>288</v>
+        <v>316</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P7" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -1863,43 +1866,43 @@
         <v>177</v>
       </c>
       <c r="D8" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E8" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F8" t="s">
+        <v>289</v>
+      </c>
+      <c r="G8" t="s">
+        <v>326</v>
+      </c>
+      <c r="H8" t="s">
         <v>295</v>
       </c>
-      <c r="G8" t="s">
-        <v>333</v>
-      </c>
-      <c r="H8" t="s">
-        <v>301</v>
-      </c>
       <c r="I8" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J8" s="5">
         <v>39599</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L8" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M8" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N8" t="s">
-        <v>325</v>
-      </c>
-      <c r="O8" t="s">
-        <v>288</v>
+        <v>318</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P8" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -1913,43 +1916,43 @@
         <v>178</v>
       </c>
       <c r="D9" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E9" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F9" t="s">
+        <v>289</v>
+      </c>
+      <c r="G9" t="s">
+        <v>330</v>
+      </c>
+      <c r="H9" t="s">
         <v>295</v>
       </c>
-      <c r="G9" t="s">
-        <v>337</v>
-      </c>
-      <c r="H9" t="s">
-        <v>301</v>
-      </c>
       <c r="I9" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J9" s="6">
         <v>34458</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L9" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M9" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N9" t="s">
-        <v>323</v>
-      </c>
-      <c r="O9" t="s">
-        <v>288</v>
+        <v>316</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P9" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
@@ -1963,43 +1966,43 @@
         <v>179</v>
       </c>
       <c r="D10" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E10" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F10" t="s">
+        <v>289</v>
+      </c>
+      <c r="G10" t="s">
+        <v>326</v>
+      </c>
+      <c r="H10" t="s">
         <v>295</v>
       </c>
-      <c r="G10" t="s">
-        <v>333</v>
-      </c>
-      <c r="H10" t="s">
-        <v>301</v>
-      </c>
       <c r="I10" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J10" s="6">
         <v>32998</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L10" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M10" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N10" t="s">
-        <v>324</v>
-      </c>
-      <c r="O10" t="s">
-        <v>288</v>
+        <v>317</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P10" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
@@ -2013,43 +2016,43 @@
         <v>180</v>
       </c>
       <c r="D11" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E11" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F11" t="s">
+        <v>289</v>
+      </c>
+      <c r="G11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H11" t="s">
         <v>295</v>
       </c>
-      <c r="G11" t="s">
-        <v>334</v>
-      </c>
-      <c r="H11" t="s">
-        <v>301</v>
-      </c>
       <c r="I11" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J11" s="5">
         <v>40650</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L11" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M11" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N11" t="s">
-        <v>325</v>
-      </c>
-      <c r="O11" t="s">
-        <v>288</v>
+        <v>318</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P11" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -2063,43 +2066,43 @@
         <v>181</v>
       </c>
       <c r="D12" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E12" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F12" t="s">
+        <v>289</v>
+      </c>
+      <c r="G12" t="s">
+        <v>325</v>
+      </c>
+      <c r="H12" t="s">
         <v>295</v>
       </c>
-      <c r="G12" t="s">
-        <v>332</v>
-      </c>
-      <c r="H12" t="s">
-        <v>301</v>
-      </c>
       <c r="I12" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J12" s="5">
         <v>28332</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L12" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M12" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N12" t="s">
-        <v>323</v>
-      </c>
-      <c r="O12" t="s">
-        <v>288</v>
+        <v>316</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P12" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
@@ -2113,43 +2116,43 @@
         <v>182</v>
       </c>
       <c r="D13" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E13" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F13" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G13" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H13" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I13" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J13" s="5">
         <v>23013</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L13" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M13" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N13" t="s">
-        <v>323</v>
-      </c>
-      <c r="O13" t="s">
-        <v>288</v>
+        <v>316</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P13" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -2163,43 +2166,43 @@
         <v>183</v>
       </c>
       <c r="D14" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E14" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F14" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G14" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H14" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I14" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J14" s="5">
         <v>28182</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L14" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M14" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N14" t="s">
-        <v>324</v>
-      </c>
-      <c r="O14" t="s">
-        <v>288</v>
+        <v>317</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P14" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -2213,43 +2216,43 @@
         <v>184</v>
       </c>
       <c r="D15" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E15" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F15" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G15" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H15" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I15" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J15" s="5">
         <v>35768</v>
       </c>
       <c r="K15" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L15" t="s">
         <v>315</v>
       </c>
-      <c r="L15" t="s">
-        <v>322</v>
-      </c>
       <c r="M15" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N15" t="s">
-        <v>325</v>
-      </c>
-      <c r="O15" t="s">
-        <v>288</v>
+        <v>318</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P15" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
@@ -2263,43 +2266,43 @@
         <v>185</v>
       </c>
       <c r="D16" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E16" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G16" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H16" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I16" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J16" s="5">
         <v>43213</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L16" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M16" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N16" t="s">
-        <v>325</v>
-      </c>
-      <c r="O16" t="s">
-        <v>288</v>
+        <v>318</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>342</v>
       </c>
       <c r="P16" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
@@ -2313,43 +2316,43 @@
         <v>186</v>
       </c>
       <c r="D17" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E17" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F17" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G17" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H17" t="s">
         <v>277</v>
       </c>
       <c r="I17" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J17" s="5">
         <v>20645</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L17" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M17" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N17" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P17" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
@@ -2363,43 +2366,43 @@
         <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E18" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F18" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G18" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H18" t="s">
         <v>277</v>
       </c>
       <c r="I18" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J18" s="5">
         <v>30915</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L18" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M18" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N18" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P18" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
@@ -2413,43 +2416,43 @@
         <v>188</v>
       </c>
       <c r="D19" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E19" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F19" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G19" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H19" t="s">
         <v>277</v>
       </c>
       <c r="I19" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J19" s="5">
         <v>30545</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L19" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M19" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N19" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P19" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -2463,43 +2466,43 @@
         <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E20" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F20" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G20" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H20" t="s">
         <v>277</v>
       </c>
       <c r="I20" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J20" s="5">
         <v>39273</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L20" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M20" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N20" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P20" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -2510,46 +2513,46 @@
         <v>3171041521190010</v>
       </c>
       <c r="C21" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D21" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E21" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F21" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G21" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H21" t="s">
         <v>277</v>
       </c>
       <c r="I21" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J21" s="5">
         <v>36841</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L21" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M21" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N21" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P21" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -2563,43 +2566,43 @@
         <v>190</v>
       </c>
       <c r="D22" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E22" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F22" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G22" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H22" t="s">
         <v>277</v>
       </c>
       <c r="I22" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J22" s="5">
         <v>23540</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L22" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M22" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N22" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P22" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
@@ -2613,43 +2616,43 @@
         <v>191</v>
       </c>
       <c r="D23" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E23" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F23" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G23" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H23" t="s">
         <v>277</v>
       </c>
       <c r="I23" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J23" s="5">
         <v>29300</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L23" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M23" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N23" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P23" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -2663,43 +2666,43 @@
         <v>192</v>
       </c>
       <c r="D24" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E24" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F24" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G24" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H24" t="s">
         <v>278</v>
       </c>
       <c r="I24" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J24" s="5">
         <v>45039</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L24" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M24" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="N24" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P24" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
@@ -2713,43 +2716,43 @@
         <v>193</v>
       </c>
       <c r="D25" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E25" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F25" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G25" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H25" t="s">
         <v>278</v>
       </c>
       <c r="I25" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J25" s="5">
         <v>36707</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L25" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M25" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N25" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P25" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
@@ -2763,43 +2766,43 @@
         <v>194</v>
       </c>
       <c r="D26" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E26" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F26" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G26" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H26" t="s">
         <v>278</v>
       </c>
       <c r="I26" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J26" s="5">
         <v>40698</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L26" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M26" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N26" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P26" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -2813,43 +2816,43 @@
         <v>195</v>
       </c>
       <c r="D27" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E27" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F27" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G27" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H27" t="s">
         <v>278</v>
       </c>
       <c r="I27" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J27" s="5">
         <v>37812</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L27" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M27" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N27" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P27" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -2863,43 +2866,43 @@
         <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E28" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F28" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G28" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H28" t="s">
         <v>278</v>
       </c>
       <c r="I28" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J28" s="5">
         <v>38822</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L28" t="s">
+        <v>315</v>
+      </c>
+      <c r="M28" t="s">
         <v>322</v>
       </c>
-      <c r="M28" t="s">
-        <v>329</v>
-      </c>
       <c r="N28" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P28" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
@@ -2913,43 +2916,43 @@
         <v>197</v>
       </c>
       <c r="D29" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E29" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F29" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G29" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H29" t="s">
         <v>279</v>
       </c>
       <c r="I29" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J29" s="5">
         <v>18500</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L29" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M29" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N29" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P29" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
@@ -2963,43 +2966,43 @@
         <v>198</v>
       </c>
       <c r="D30" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E30" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F30" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G30" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H30" t="s">
         <v>279</v>
       </c>
       <c r="I30" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J30" s="5">
         <v>38777</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L30" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M30" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N30" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P30" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -3013,43 +3016,43 @@
         <v>199</v>
       </c>
       <c r="D31" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E31" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F31" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G31" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H31" t="s">
         <v>279</v>
       </c>
       <c r="I31" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J31" s="5">
         <v>40320</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L31" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N31" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="P31" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
@@ -3063,43 +3066,43 @@
         <v>200</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E32" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F32" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G32" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H32" t="s">
         <v>279</v>
       </c>
       <c r="I32" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J32" s="5">
         <v>28561</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L32" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N32" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P32" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -3113,43 +3116,43 @@
         <v>201</v>
       </c>
       <c r="D33" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E33" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F33" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G33" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H33" t="s">
         <v>279</v>
       </c>
       <c r="I33" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J33" s="5">
         <v>32314</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L33" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M33" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N33" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P33" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
@@ -3163,43 +3166,43 @@
         <v>202</v>
       </c>
       <c r="D34" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E34" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F34" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G34" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H34" t="s">
         <v>279</v>
       </c>
       <c r="I34" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J34" s="5">
         <v>38823</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L34" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M34" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P34" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
@@ -3213,43 +3216,43 @@
         <v>203</v>
       </c>
       <c r="D35" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E35" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F35" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G35" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H35" t="s">
         <v>279</v>
       </c>
       <c r="I35" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J35" s="5">
         <v>38067</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L35" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P35" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
@@ -3263,43 +3266,43 @@
         <v>204</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E36" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F36" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G36" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H36" t="s">
         <v>279</v>
       </c>
       <c r="I36" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J36" s="5">
         <v>38604</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L36" t="s">
+        <v>315</v>
+      </c>
+      <c r="M36" t="s">
         <v>322</v>
       </c>
-      <c r="M36" t="s">
-        <v>329</v>
-      </c>
       <c r="N36" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P36" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
@@ -3313,43 +3316,43 @@
         <v>205</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E37" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F37" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G37" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H37" t="s">
         <v>279</v>
       </c>
       <c r="I37" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J37" s="5">
         <v>27494</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L37" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N37" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
@@ -3363,43 +3366,43 @@
         <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E38" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F38" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G38" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H38" t="s">
         <v>279</v>
       </c>
       <c r="I38" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J38" s="5">
         <v>28836</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L38" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N38" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O38" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P38" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
@@ -3413,43 +3416,43 @@
         <v>207</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E39" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F39" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G39" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H39" t="s">
         <v>279</v>
       </c>
       <c r="I39" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J39" s="5">
         <v>37339</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L39" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M39" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N39" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P39" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
@@ -3463,43 +3466,43 @@
         <v>208</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E40" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F40" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G40" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H40" t="s">
         <v>279</v>
       </c>
       <c r="I40" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J40" s="5">
         <v>29368</v>
       </c>
       <c r="K40" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L40" t="s">
         <v>315</v>
       </c>
-      <c r="L40" t="s">
-        <v>322</v>
-      </c>
       <c r="M40" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N40" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O40" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P40" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
@@ -3513,43 +3516,43 @@
         <v>209</v>
       </c>
       <c r="D41" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E41" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F41" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G41" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H41" t="s">
         <v>279</v>
       </c>
       <c r="I41" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J41" s="5">
         <v>44353</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L41" t="s">
+        <v>315</v>
+      </c>
+      <c r="M41" t="s">
         <v>322</v>
       </c>
-      <c r="M41" t="s">
-        <v>329</v>
-      </c>
       <c r="N41" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="P41" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
@@ -3563,43 +3566,43 @@
         <v>210</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E42" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F42" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G42" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H42" t="s">
         <v>279</v>
       </c>
       <c r="I42" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J42" s="5">
         <v>23847</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L42" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M42" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="N42" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O42" s="9" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="P42" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
@@ -3613,43 +3616,43 @@
         <v>211</v>
       </c>
       <c r="D43" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E43" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F43" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G43" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H43" t="s">
         <v>279</v>
       </c>
       <c r="I43" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J43" s="5">
         <v>24168</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L43" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M43" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N43" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="P43" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
@@ -3663,43 +3666,43 @@
         <v>212</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E44" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F44" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G44" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H44" t="s">
         <v>279</v>
       </c>
       <c r="I44" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J44" s="5">
         <v>36096</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L44" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N44" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="P44" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
@@ -3713,43 +3716,43 @@
         <v>213</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E45" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F45" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G45" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H45" t="s">
         <v>279</v>
       </c>
       <c r="I45" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J45" s="5">
         <v>37434</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L45" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M45" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N45" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="P45" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
@@ -3763,43 +3766,43 @@
         <v>214</v>
       </c>
       <c r="D46" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E46" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F46" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G46" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H46" t="s">
         <v>279</v>
       </c>
       <c r="I46" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J46" s="5">
         <v>17203</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L46" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M46" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N46" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="O46" s="9" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="P46" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
@@ -3813,43 +3816,43 @@
         <v>215</v>
       </c>
       <c r="D47" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E47" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F47" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G47" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H47" t="s">
         <v>279</v>
       </c>
       <c r="I47" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J47" s="5">
         <v>29422</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L47" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M47" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N47" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="P47" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
@@ -3863,43 +3866,43 @@
         <v>216</v>
       </c>
       <c r="D48" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E48" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F48" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G48" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H48" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I48" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J48" s="5">
         <v>24330</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L48" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M48" t="s">
+        <v>333</v>
+      </c>
+      <c r="N48" t="s">
+        <v>316</v>
+      </c>
+      <c r="O48" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="N48" t="s">
-        <v>323</v>
-      </c>
-      <c r="O48" t="s">
-        <v>289</v>
-      </c>
       <c r="P48" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
@@ -3913,43 +3916,43 @@
         <v>217</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E49" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F49" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G49" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H49" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I49" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J49" s="5">
         <v>26584</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L49" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M49" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N49" t="s">
-        <v>324</v>
-      </c>
-      <c r="O49" t="s">
-        <v>289</v>
+        <v>317</v>
+      </c>
+      <c r="O49" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P49" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
@@ -3963,43 +3966,43 @@
         <v>218</v>
       </c>
       <c r="D50" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E50" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F50" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G50" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H50" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I50" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J50" s="5">
         <v>39818</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L50" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M50" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N50" t="s">
-        <v>325</v>
-      </c>
-      <c r="O50" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O50" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P50" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
@@ -4013,43 +4016,43 @@
         <v>219</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E51" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F51" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G51" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H51" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I51" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J51" s="5">
         <v>36600</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L51" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M51" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N51" t="s">
-        <v>325</v>
-      </c>
-      <c r="O51" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P51" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
@@ -4063,43 +4066,43 @@
         <v>220</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E52" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F52" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G52" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H52" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I52" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J52" s="5">
         <v>41847</v>
       </c>
       <c r="K52" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L52" t="s">
         <v>315</v>
       </c>
-      <c r="L52" t="s">
+      <c r="M52" t="s">
         <v>322</v>
       </c>
-      <c r="M52" t="s">
-        <v>329</v>
-      </c>
       <c r="N52" t="s">
-        <v>325</v>
-      </c>
-      <c r="O52" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O52" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P52" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
@@ -4113,43 +4116,43 @@
         <v>221</v>
       </c>
       <c r="D53" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E53" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F53" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G53" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H53" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I53" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J53" s="5">
         <v>42923</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L53" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M53" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N53" t="s">
-        <v>325</v>
-      </c>
-      <c r="O53" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O53" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P53" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
@@ -4163,43 +4166,43 @@
         <v>222</v>
       </c>
       <c r="D54" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E54" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F54" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G54" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H54" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I54" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J54" s="5">
         <v>29353</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L54" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M54" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N54" t="s">
-        <v>323</v>
-      </c>
-      <c r="O54" t="s">
-        <v>289</v>
+        <v>316</v>
+      </c>
+      <c r="O54" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P54" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
@@ -4213,43 +4216,43 @@
         <v>223</v>
       </c>
       <c r="D55" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E55" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F55" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G55" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H55" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I55" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J55" s="5">
         <v>32580</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L55" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M55" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N55" t="s">
-        <v>324</v>
-      </c>
-      <c r="O55" t="s">
-        <v>289</v>
+        <v>317</v>
+      </c>
+      <c r="O55" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P55" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
@@ -4263,43 +4266,43 @@
         <v>224</v>
       </c>
       <c r="D56" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E56" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F56" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G56" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H56" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I56" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J56" s="5">
         <v>40850</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L56" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M56" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N56" t="s">
-        <v>325</v>
-      </c>
-      <c r="O56" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O56" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P56" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
@@ -4313,43 +4316,43 @@
         <v>225</v>
       </c>
       <c r="D57" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E57" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F57" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G57" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H57" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I57" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J57" s="6">
         <v>41932</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L57" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M57" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N57" t="s">
-        <v>325</v>
-      </c>
-      <c r="O57" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O57" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P57" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
@@ -4363,43 +4366,43 @@
         <v>226</v>
       </c>
       <c r="D58" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E58" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F58" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G58" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H58" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I58" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J58" s="5">
         <v>43827</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L58" t="s">
+        <v>315</v>
+      </c>
+      <c r="M58" t="s">
         <v>322</v>
       </c>
-      <c r="M58" t="s">
-        <v>329</v>
-      </c>
       <c r="N58" t="s">
-        <v>325</v>
-      </c>
-      <c r="O58" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O58" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P58" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
@@ -4413,43 +4416,43 @@
         <v>227</v>
       </c>
       <c r="D59" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E59" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F59" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G59" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H59" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I59" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J59" s="5">
         <v>23115</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L59" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M59" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N59" t="s">
-        <v>325</v>
-      </c>
-      <c r="O59" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O59" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P59" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
@@ -4463,43 +4466,43 @@
         <v>228</v>
       </c>
       <c r="D60" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E60" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F60" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G60" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="H60" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I60" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J60" s="5">
         <v>31255</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L60" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M60" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N60" t="s">
-        <v>323</v>
-      </c>
-      <c r="O60" t="s">
-        <v>289</v>
+        <v>316</v>
+      </c>
+      <c r="O60" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P60" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
@@ -4513,43 +4516,43 @@
         <v>229</v>
       </c>
       <c r="D61" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E61" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F61" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G61" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H61" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I61" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J61" s="5">
         <v>31535</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L61" t="s">
+        <v>314</v>
+      </c>
+      <c r="M61" t="s">
         <v>321</v>
       </c>
-      <c r="M61" t="s">
-        <v>328</v>
-      </c>
       <c r="N61" t="s">
-        <v>324</v>
-      </c>
-      <c r="O61" t="s">
-        <v>289</v>
+        <v>317</v>
+      </c>
+      <c r="O61" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P61" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
@@ -4563,43 +4566,43 @@
         <v>230</v>
       </c>
       <c r="D62" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E62" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F62" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G62" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H62" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I62" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J62" s="5">
         <v>40239</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L62" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M62" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N62" t="s">
-        <v>325</v>
-      </c>
-      <c r="O62" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O62" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P62" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
@@ -4613,43 +4616,43 @@
         <v>231</v>
       </c>
       <c r="D63" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E63" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F63" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G63" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="H63" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="I63" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J63" s="5">
         <v>27713</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L63" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M63" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N63" t="s">
-        <v>323</v>
-      </c>
-      <c r="O63" t="s">
-        <v>289</v>
+        <v>316</v>
+      </c>
+      <c r="O63" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P63" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
@@ -4663,43 +4666,43 @@
         <v>232</v>
       </c>
       <c r="D64" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E64" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F64" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G64" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H64" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I64" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J64" s="5">
         <v>29957</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L64" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M64" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N64" t="s">
-        <v>324</v>
-      </c>
-      <c r="O64" t="s">
-        <v>289</v>
+        <v>317</v>
+      </c>
+      <c r="O64" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P64" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
@@ -4713,43 +4716,43 @@
         <v>233</v>
       </c>
       <c r="D65" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E65" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F65" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G65" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H65" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="I65" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J65" s="5">
         <v>39303</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L65" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M65" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N65" t="s">
-        <v>325</v>
-      </c>
-      <c r="O65" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O65" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P65" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
@@ -4763,43 +4766,43 @@
         <v>234</v>
       </c>
       <c r="D66" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E66" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F66" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G66" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H66" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I66" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J66" s="5">
         <v>40689</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L66" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M66" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N66" t="s">
-        <v>325</v>
-      </c>
-      <c r="O66" t="s">
-        <v>289</v>
+        <v>318</v>
+      </c>
+      <c r="O66" s="9" t="s">
+        <v>340</v>
       </c>
       <c r="P66" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
@@ -4813,43 +4816,43 @@
         <v>235</v>
       </c>
       <c r="D67" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E67" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F67" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G67" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H67" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="I67" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J67" s="5">
         <v>19770</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L67" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M67" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N67" t="s">
-        <v>323</v>
-      </c>
-      <c r="O67" t="s">
-        <v>290</v>
+        <v>316</v>
+      </c>
+      <c r="O67" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P67" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
@@ -4863,43 +4866,43 @@
         <v>236</v>
       </c>
       <c r="D68" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E68" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F68" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G68" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H68" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="I68" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J68" s="5">
         <v>24117</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L68" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M68" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N68" t="s">
-        <v>324</v>
-      </c>
-      <c r="O68" t="s">
-        <v>290</v>
+        <v>317</v>
+      </c>
+      <c r="O68" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P68" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
@@ -4913,43 +4916,43 @@
         <v>237</v>
       </c>
       <c r="D69" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E69" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F69" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G69" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H69" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="I69" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J69" s="5">
         <v>11158</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L69" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M69" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N69" t="s">
-        <v>323</v>
-      </c>
-      <c r="O69" t="s">
-        <v>290</v>
+        <v>316</v>
+      </c>
+      <c r="O69" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P69" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
@@ -4963,43 +4966,43 @@
         <v>238</v>
       </c>
       <c r="D70" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E70" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F70" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G70" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H70" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="I70" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J70" s="5">
         <v>36636</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L70" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M70" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N70" t="s">
-        <v>324</v>
-      </c>
-      <c r="O70" t="s">
-        <v>290</v>
+        <v>317</v>
+      </c>
+      <c r="O70" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P70" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
@@ -5013,43 +5016,43 @@
         <v>239</v>
       </c>
       <c r="D71" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E71" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F71" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G71" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H71" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I71" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J71" s="5">
         <v>23294</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L71" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M71" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="N71" t="s">
-        <v>323</v>
-      </c>
-      <c r="O71" t="s">
-        <v>290</v>
+        <v>316</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P71" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
@@ -5063,43 +5066,43 @@
         <v>240</v>
       </c>
       <c r="D72" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E72" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F72" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G72" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H72" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I72" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J72" s="5">
         <v>24303</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L72" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M72" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N72" t="s">
-        <v>324</v>
-      </c>
-      <c r="O72" t="s">
-        <v>290</v>
+        <v>317</v>
+      </c>
+      <c r="O72" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P72" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
@@ -5113,43 +5116,43 @@
         <v>241</v>
       </c>
       <c r="D73" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E73" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F73" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G73" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H73" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I73" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J73" s="5">
         <v>36007</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L73" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M73" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N73" t="s">
-        <v>325</v>
-      </c>
-      <c r="O73" t="s">
-        <v>290</v>
+        <v>318</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
@@ -5163,43 +5166,43 @@
         <v>242</v>
       </c>
       <c r="D74" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E74" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F74" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G74" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H74" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I74" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J74" s="5">
         <v>26958</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L74" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M74" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N74" t="s">
-        <v>323</v>
-      </c>
-      <c r="O74" t="s">
-        <v>290</v>
+        <v>316</v>
+      </c>
+      <c r="O74" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P74" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
@@ -5213,43 +5216,43 @@
         <v>243</v>
       </c>
       <c r="D75" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E75" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F75" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G75" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H75" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I75" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J75" s="5">
         <v>30799</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L75" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M75" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N75" t="s">
-        <v>324</v>
-      </c>
-      <c r="O75" t="s">
-        <v>290</v>
+        <v>317</v>
+      </c>
+      <c r="O75" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P75" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
@@ -5263,43 +5266,43 @@
         <v>244</v>
       </c>
       <c r="D76" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E76" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F76" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G76" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H76" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I76" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J76" s="5">
         <v>36992</v>
       </c>
       <c r="K76" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L76" t="s">
         <v>315</v>
       </c>
-      <c r="L76" t="s">
-        <v>322</v>
-      </c>
       <c r="M76" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N76" t="s">
-        <v>325</v>
-      </c>
-      <c r="O76" t="s">
-        <v>290</v>
+        <v>318</v>
+      </c>
+      <c r="O76" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="P76" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
@@ -5313,43 +5316,43 @@
         <v>245</v>
       </c>
       <c r="D77" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E77" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F77" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G77" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H77" t="s">
         <v>280</v>
       </c>
       <c r="I77" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J77" s="5">
         <v>20870</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L77" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M77" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N77" t="s">
-        <v>323</v>
-      </c>
-      <c r="O77" t="s">
-        <v>291</v>
+        <v>316</v>
+      </c>
+      <c r="O77" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="P77" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
@@ -5363,43 +5366,43 @@
         <v>246</v>
       </c>
       <c r="D78" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E78" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F78" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G78" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H78" t="s">
         <v>280</v>
       </c>
       <c r="I78" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J78" s="5">
         <v>23479</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L78" t="s">
+        <v>314</v>
+      </c>
+      <c r="M78" t="s">
         <v>321</v>
       </c>
-      <c r="M78" t="s">
-        <v>328</v>
-      </c>
       <c r="N78" t="s">
-        <v>324</v>
-      </c>
-      <c r="O78" t="s">
-        <v>291</v>
+        <v>317</v>
+      </c>
+      <c r="O78" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="P78" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
@@ -5413,43 +5416,43 @@
         <v>247</v>
       </c>
       <c r="D79" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E79" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F79" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G79" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H79" t="s">
         <v>280</v>
       </c>
       <c r="I79" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J79" s="5">
         <v>23234</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L79" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M79" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N79" t="s">
-        <v>323</v>
-      </c>
-      <c r="O79" t="s">
-        <v>291</v>
+        <v>316</v>
+      </c>
+      <c r="O79" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="P79" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.3">
@@ -5463,43 +5466,43 @@
         <v>248</v>
       </c>
       <c r="D80" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E80" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F80" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G80" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H80" t="s">
         <v>280</v>
       </c>
       <c r="I80" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J80" s="5">
         <v>19210</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L80" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M80" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N80" t="s">
-        <v>324</v>
-      </c>
-      <c r="O80" t="s">
-        <v>291</v>
+        <v>317</v>
+      </c>
+      <c r="O80" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="P80" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
@@ -5513,43 +5516,43 @@
         <v>249</v>
       </c>
       <c r="D81" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E81" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F81" t="s">
+        <v>324</v>
+      </c>
+      <c r="G81" t="s">
         <v>331</v>
-      </c>
-      <c r="G81" t="s">
-        <v>338</v>
       </c>
       <c r="H81" t="s">
         <v>280</v>
       </c>
       <c r="I81" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J81" s="5">
         <v>29956</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L81" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M81" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N81" t="s">
-        <v>323</v>
-      </c>
-      <c r="O81" t="s">
-        <v>291</v>
+        <v>316</v>
+      </c>
+      <c r="O81" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="P81" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
@@ -5563,43 +5566,43 @@
         <v>250</v>
       </c>
       <c r="D82" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E82" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F82" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G82" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H82" t="s">
         <v>280</v>
       </c>
       <c r="I82" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J82" s="5">
         <v>29507</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L82" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M82" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N82" t="s">
-        <v>324</v>
-      </c>
-      <c r="O82" t="s">
-        <v>291</v>
+        <v>317</v>
+      </c>
+      <c r="O82" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="P82" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
@@ -5613,43 +5616,43 @@
         <v>251</v>
       </c>
       <c r="D83" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E83" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F83" t="s">
+        <v>324</v>
+      </c>
+      <c r="G83" t="s">
         <v>331</v>
-      </c>
-      <c r="G83" t="s">
-        <v>338</v>
       </c>
       <c r="H83" t="s">
         <v>280</v>
       </c>
       <c r="I83" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J83" s="5">
         <v>23350</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L83" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M83" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N83" t="s">
-        <v>323</v>
-      </c>
-      <c r="O83" t="s">
-        <v>291</v>
+        <v>316</v>
+      </c>
+      <c r="O83" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="P83" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
@@ -5663,43 +5666,43 @@
         <v>252</v>
       </c>
       <c r="D84" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E84" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F84" t="s">
+        <v>324</v>
+      </c>
+      <c r="G84" t="s">
         <v>331</v>
-      </c>
-      <c r="G84" t="s">
-        <v>338</v>
       </c>
       <c r="H84" t="s">
         <v>281</v>
       </c>
       <c r="I84" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J84" s="5">
         <v>38110</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L84" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M84" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N84" t="s">
-        <v>323</v>
-      </c>
-      <c r="O84" t="s">
-        <v>287</v>
+        <v>316</v>
+      </c>
+      <c r="O84" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P84" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
@@ -5713,43 +5716,43 @@
         <v>253</v>
       </c>
       <c r="D85" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E85" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F85" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G85" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H85" t="s">
         <v>281</v>
       </c>
       <c r="I85" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J85" s="5">
         <v>33739</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L85" t="s">
+        <v>314</v>
+      </c>
+      <c r="M85" t="s">
         <v>321</v>
       </c>
-      <c r="M85" t="s">
-        <v>328</v>
-      </c>
       <c r="N85" t="s">
-        <v>324</v>
-      </c>
-      <c r="O85" t="s">
-        <v>287</v>
+        <v>317</v>
+      </c>
+      <c r="O85" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P85" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
@@ -5763,43 +5766,43 @@
         <v>254</v>
       </c>
       <c r="D86" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E86" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F86" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G86" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H86" t="s">
         <v>281</v>
       </c>
       <c r="I86" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J86" s="5">
         <v>33285</v>
       </c>
       <c r="K86" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L86" t="s">
         <v>315</v>
       </c>
-      <c r="L86" t="s">
-        <v>322</v>
-      </c>
       <c r="M86" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N86" t="s">
-        <v>325</v>
-      </c>
-      <c r="O86" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O86" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P86" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
@@ -5813,43 +5816,43 @@
         <v>255</v>
       </c>
       <c r="D87" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E87" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F87" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G87" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H87" t="s">
         <v>281</v>
       </c>
       <c r="I87" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J87" s="8">
         <v>38552</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L87" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M87" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N87" t="s">
-        <v>325</v>
-      </c>
-      <c r="O87" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O87" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P87" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
@@ -5863,43 +5866,43 @@
         <v>256</v>
       </c>
       <c r="D88" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E88" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F88" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G88" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H88" t="s">
         <v>282</v>
       </c>
       <c r="I88" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J88" s="5">
         <v>33350</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L88" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M88" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N88" t="s">
-        <v>323</v>
-      </c>
-      <c r="O88" t="s">
-        <v>287</v>
+        <v>316</v>
+      </c>
+      <c r="O88" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P88" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
@@ -5913,43 +5916,43 @@
         <v>257</v>
       </c>
       <c r="D89" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E89" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F89" t="s">
+        <v>324</v>
+      </c>
+      <c r="G89" t="s">
         <v>331</v>
-      </c>
-      <c r="G89" t="s">
-        <v>338</v>
       </c>
       <c r="H89" t="s">
         <v>283</v>
       </c>
       <c r="I89" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J89" s="5">
         <v>38969</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L89" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M89" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N89" t="s">
-        <v>323</v>
-      </c>
-      <c r="O89" t="s">
-        <v>287</v>
+        <v>316</v>
+      </c>
+      <c r="O89" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P89" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
@@ -5963,43 +5966,43 @@
         <v>258</v>
       </c>
       <c r="D90" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E90" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F90" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G90" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H90" t="s">
         <v>283</v>
       </c>
       <c r="I90" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J90" s="5">
         <v>31943</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L90" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M90" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N90" t="s">
-        <v>324</v>
-      </c>
-      <c r="O90" t="s">
-        <v>287</v>
+        <v>317</v>
+      </c>
+      <c r="O90" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P90" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
@@ -6013,43 +6016,43 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E91" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F91" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G91" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H91" t="s">
         <v>283</v>
       </c>
       <c r="I91" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J91" s="5">
         <v>40654</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L91" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M91" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N91" t="s">
-        <v>325</v>
-      </c>
-      <c r="O91" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O91" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P91" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
@@ -6063,43 +6066,43 @@
         <v>260</v>
       </c>
       <c r="D92" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E92" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F92" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G92" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="H92" t="s">
         <v>281</v>
       </c>
       <c r="I92" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J92" s="5">
         <v>29373</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L92" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M92" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N92" t="s">
-        <v>323</v>
-      </c>
-      <c r="O92" t="s">
-        <v>291</v>
+        <v>316</v>
+      </c>
+      <c r="O92" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P92" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
@@ -6113,43 +6116,43 @@
         <v>261</v>
       </c>
       <c r="D93" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E93" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F93" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G93" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H93" t="s">
         <v>281</v>
       </c>
       <c r="I93" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J93" s="5">
         <v>38938</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L93" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M93" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N93" t="s">
-        <v>324</v>
-      </c>
-      <c r="O93" t="s">
-        <v>291</v>
+        <v>317</v>
+      </c>
+      <c r="O93" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P93" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
@@ -6163,43 +6166,43 @@
         <v>262</v>
       </c>
       <c r="D94" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E94" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F94" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G94" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H94" t="s">
         <v>281</v>
       </c>
       <c r="I94" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J94" s="5">
         <v>36713</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L94" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M94" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N94" t="s">
-        <v>325</v>
-      </c>
-      <c r="O94" t="s">
-        <v>291</v>
+        <v>318</v>
+      </c>
+      <c r="O94" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P94" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
@@ -6213,43 +6216,43 @@
         <v>263</v>
       </c>
       <c r="D95" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E95" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F95" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G95" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H95" t="s">
         <v>284</v>
       </c>
       <c r="I95" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J95" s="5">
         <v>36747</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L95" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M95" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N95" t="s">
-        <v>323</v>
-      </c>
-      <c r="O95" t="s">
-        <v>287</v>
+        <v>316</v>
+      </c>
+      <c r="O95" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P95" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
@@ -6260,46 +6263,46 @@
         <v>153</v>
       </c>
       <c r="C96" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D96" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E96" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F96" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G96" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H96" t="s">
         <v>284</v>
       </c>
       <c r="I96" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J96" s="5">
         <v>39303</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L96" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M96" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N96" t="s">
-        <v>324</v>
-      </c>
-      <c r="O96" t="s">
-        <v>287</v>
+        <v>317</v>
+      </c>
+      <c r="O96" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P96" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
@@ -6313,43 +6316,43 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E97" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F97" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G97" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H97" t="s">
         <v>284</v>
       </c>
       <c r="I97" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J97" s="5">
         <v>38938</v>
       </c>
       <c r="K97" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L97" t="s">
         <v>315</v>
       </c>
-      <c r="L97" t="s">
-        <v>322</v>
-      </c>
       <c r="M97" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N97" t="s">
-        <v>325</v>
-      </c>
-      <c r="O97" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O97" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P97" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
@@ -6363,43 +6366,43 @@
         <v>265</v>
       </c>
       <c r="D98" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E98" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F98" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G98" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H98" t="s">
         <v>281</v>
       </c>
       <c r="I98" t="s">
+        <v>310</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="L98" t="s">
+        <v>314</v>
+      </c>
+      <c r="M98" t="s">
+        <v>319</v>
+      </c>
+      <c r="N98" t="s">
         <v>316</v>
       </c>
-      <c r="J98" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="L98" t="s">
-        <v>321</v>
-      </c>
-      <c r="M98" t="s">
-        <v>326</v>
-      </c>
-      <c r="N98" t="s">
-        <v>323</v>
-      </c>
-      <c r="O98" t="s">
-        <v>287</v>
+      <c r="O98" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P98" s="9" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
@@ -6413,43 +6416,43 @@
         <v>266</v>
       </c>
       <c r="D99" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E99" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F99" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G99" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="H99" t="s">
         <v>285</v>
       </c>
       <c r="I99" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J99" s="5">
         <v>20279</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L99" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M99" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N99" t="s">
-        <v>323</v>
-      </c>
-      <c r="O99" t="s">
-        <v>287</v>
+        <v>316</v>
+      </c>
+      <c r="O99" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P99" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
@@ -6463,43 +6466,43 @@
         <v>267</v>
       </c>
       <c r="D100" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E100" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F100" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G100" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H100" t="s">
         <v>285</v>
       </c>
       <c r="I100" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J100" s="5">
         <v>30001</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L100" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M100" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N100" t="s">
-        <v>324</v>
-      </c>
-      <c r="O100" t="s">
-        <v>287</v>
+        <v>317</v>
+      </c>
+      <c r="O100" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P100" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
@@ -6513,43 +6516,43 @@
         <v>268</v>
       </c>
       <c r="D101" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E101" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F101" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G101" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H101" t="s">
         <v>285</v>
       </c>
       <c r="I101" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J101" s="5">
         <v>40167</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L101" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M101" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N101" t="s">
-        <v>325</v>
-      </c>
-      <c r="O101" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O101" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P101" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
@@ -6563,43 +6566,43 @@
         <v>269</v>
       </c>
       <c r="D102" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E102" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F102" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G102" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H102" t="s">
         <v>285</v>
       </c>
       <c r="I102" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J102" s="5">
         <v>41464</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L102" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M102" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N102" t="s">
-        <v>325</v>
-      </c>
-      <c r="O102" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O102" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P102" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
@@ -6613,43 +6616,43 @@
         <v>270</v>
       </c>
       <c r="D103" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E103" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F103" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G103" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H103" t="s">
         <v>286</v>
       </c>
       <c r="I103" t="s">
+        <v>310</v>
+      </c>
+      <c r="J103" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="K103" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L103" t="s">
+        <v>314</v>
+      </c>
+      <c r="M103" t="s">
+        <v>319</v>
+      </c>
+      <c r="N103" t="s">
         <v>316</v>
       </c>
-      <c r="J103" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="K103" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="L103" t="s">
-        <v>321</v>
-      </c>
-      <c r="M103" t="s">
-        <v>326</v>
-      </c>
-      <c r="N103" t="s">
-        <v>323</v>
-      </c>
-      <c r="O103" t="s">
-        <v>287</v>
+      <c r="O103" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P103" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
@@ -6663,43 +6666,43 @@
         <v>271</v>
       </c>
       <c r="D104" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E104" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F104" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G104" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H104" t="s">
         <v>286</v>
       </c>
       <c r="I104" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J104" s="5">
         <v>33276</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L104" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M104" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N104" t="s">
-        <v>324</v>
-      </c>
-      <c r="O104" t="s">
-        <v>287</v>
+        <v>317</v>
+      </c>
+      <c r="O104" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P104" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
@@ -6713,43 +6716,43 @@
         <v>272</v>
       </c>
       <c r="D105" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E105" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F105" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G105" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H105" t="s">
         <v>286</v>
       </c>
       <c r="I105" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J105" s="5">
         <v>36713</v>
       </c>
       <c r="K105" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L105" t="s">
         <v>315</v>
       </c>
-      <c r="L105" t="s">
-        <v>322</v>
-      </c>
       <c r="M105" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N105" t="s">
-        <v>325</v>
-      </c>
-      <c r="O105" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O105" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P105" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
@@ -6763,43 +6766,43 @@
         <v>273</v>
       </c>
       <c r="D106" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E106" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F106" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G106" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H106" t="s">
         <v>286</v>
       </c>
       <c r="I106" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J106" s="5">
         <v>36399</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L106" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M106" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N106" t="s">
-        <v>325</v>
-      </c>
-      <c r="O106" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O106" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P106" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
@@ -6813,43 +6816,43 @@
         <v>274</v>
       </c>
       <c r="D107" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E107" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F107" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G107" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H107" t="s">
         <v>286</v>
       </c>
       <c r="I107" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J107" s="5">
         <v>36940</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L107" t="s">
+        <v>315</v>
+      </c>
+      <c r="M107" t="s">
         <v>322</v>
       </c>
-      <c r="M107" t="s">
-        <v>329</v>
-      </c>
       <c r="N107" t="s">
-        <v>325</v>
-      </c>
-      <c r="O107" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O107" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P107" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
@@ -6863,43 +6866,43 @@
         <v>157</v>
       </c>
       <c r="D108" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E108" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F108" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G108" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="H108" t="s">
         <v>275</v>
       </c>
       <c r="I108" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J108" s="5">
         <v>20361</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L108" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M108" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N108" t="s">
-        <v>323</v>
-      </c>
-      <c r="O108" t="s">
-        <v>287</v>
+        <v>316</v>
+      </c>
+      <c r="O108" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P108" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.3">
@@ -6913,43 +6916,43 @@
         <v>158</v>
       </c>
       <c r="D109" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E109" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F109" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G109" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H109" t="s">
         <v>275</v>
       </c>
       <c r="I109" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J109" s="5">
         <v>35443</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="L109" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M109" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N109" t="s">
-        <v>324</v>
-      </c>
-      <c r="O109" t="s">
-        <v>287</v>
+        <v>317</v>
+      </c>
+      <c r="O109" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P109" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.3">
@@ -6963,43 +6966,43 @@
         <v>159</v>
       </c>
       <c r="D110" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E110" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F110" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G110" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H110" t="s">
         <v>275</v>
       </c>
       <c r="I110" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J110" s="5">
         <v>36975</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L110" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M110" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N110" t="s">
-        <v>325</v>
-      </c>
-      <c r="O110" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O110" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P110" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
@@ -7013,43 +7016,43 @@
         <v>160</v>
       </c>
       <c r="D111" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E111" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F111" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G111" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H111" t="s">
         <v>275</v>
       </c>
       <c r="I111" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J111" s="5">
         <v>36075</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L111" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M111" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N111" t="s">
-        <v>323</v>
-      </c>
-      <c r="O111" t="s">
-        <v>287</v>
+        <v>316</v>
+      </c>
+      <c r="O111" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P111" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.3">
@@ -7063,43 +7066,43 @@
         <v>161</v>
       </c>
       <c r="D112" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E112" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F112" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G112" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H112" t="s">
         <v>275</v>
       </c>
       <c r="I112" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J112" s="5">
         <v>39367</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L112" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M112" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N112" t="s">
-        <v>325</v>
-      </c>
-      <c r="O112" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O112" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P112" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
@@ -7113,43 +7116,43 @@
         <v>162</v>
       </c>
       <c r="D113" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E113" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F113" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G113" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H113" t="s">
         <v>275</v>
       </c>
       <c r="I113" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J113" s="5">
         <v>40856</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L113" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M113" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N113" t="s">
-        <v>325</v>
-      </c>
-      <c r="O113" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O113" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
@@ -7163,43 +7166,43 @@
         <v>163</v>
       </c>
       <c r="D114" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E114" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F114" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G114" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H114" t="s">
         <v>275</v>
       </c>
       <c r="I114" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J114" s="5">
         <v>35147</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="L114" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M114" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="N114" t="s">
-        <v>323</v>
-      </c>
-      <c r="O114" t="s">
-        <v>287</v>
+        <v>316</v>
+      </c>
+      <c r="O114" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P114" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
@@ -7213,43 +7216,43 @@
         <v>164</v>
       </c>
       <c r="D115" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E115" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F115" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G115" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H115" t="s">
         <v>275</v>
       </c>
       <c r="I115" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J115" s="5">
         <v>30804</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L115" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M115" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N115" t="s">
-        <v>324</v>
-      </c>
-      <c r="O115" t="s">
-        <v>287</v>
+        <v>317</v>
+      </c>
+      <c r="O115" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P115" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.3">
@@ -7263,43 +7266,43 @@
         <v>165</v>
       </c>
       <c r="D116" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E116" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F116" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G116" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H116" t="s">
         <v>275</v>
       </c>
       <c r="I116" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J116" s="5">
         <v>41822</v>
       </c>
       <c r="K116" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L116" t="s">
         <v>315</v>
       </c>
-      <c r="L116" t="s">
-        <v>322</v>
-      </c>
       <c r="M116" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N116" t="s">
-        <v>325</v>
-      </c>
-      <c r="O116" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O116" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P116" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.3">
@@ -7313,43 +7316,43 @@
         <v>166</v>
       </c>
       <c r="D117" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E117" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F117" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G117" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H117" t="s">
         <v>275</v>
       </c>
       <c r="I117" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J117" s="5">
         <v>43830</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="L117" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M117" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N117" t="s">
-        <v>325</v>
-      </c>
-      <c r="O117" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O117" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P117" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
@@ -7363,43 +7366,43 @@
         <v>167</v>
       </c>
       <c r="D118" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E118" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F118" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G118" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="H118" t="s">
         <v>276</v>
       </c>
       <c r="I118" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J118" s="5">
         <v>40377</v>
       </c>
       <c r="K118" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L118" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M118" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N118" t="s">
-        <v>323</v>
-      </c>
-      <c r="O118" t="s">
-        <v>287</v>
+        <v>316</v>
+      </c>
+      <c r="O118" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P118" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
@@ -7413,43 +7416,43 @@
         <v>168</v>
       </c>
       <c r="D119" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E119" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F119" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G119" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="H119" t="s">
         <v>276</v>
       </c>
       <c r="I119" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J119" s="5">
         <v>27810</v>
       </c>
       <c r="K119" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L119" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="M119" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="N119" t="s">
-        <v>324</v>
-      </c>
-      <c r="O119" t="s">
-        <v>287</v>
+        <v>317</v>
+      </c>
+      <c r="O119" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P119" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
@@ -7463,43 +7466,43 @@
         <v>169</v>
       </c>
       <c r="D120" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E120" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F120" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G120" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H120" t="s">
         <v>276</v>
       </c>
       <c r="I120" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J120" s="5">
         <v>38604</v>
       </c>
       <c r="K120" s="7" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L120" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M120" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="N120" t="s">
-        <v>325</v>
-      </c>
-      <c r="O120" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O120" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P120" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
@@ -7513,43 +7516,43 @@
         <v>170</v>
       </c>
       <c r="D121" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E121" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="F121" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G121" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H121" t="s">
         <v>276</v>
       </c>
       <c r="I121" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="J121" s="5">
         <v>40652</v>
       </c>
       <c r="K121" s="7" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L121" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M121" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="N121" t="s">
-        <v>325</v>
-      </c>
-      <c r="O121" t="s">
-        <v>287</v>
+        <v>318</v>
+      </c>
+      <c r="O121" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="P121" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
